--- a/prep_and_checklists/Cara Brophy  /ORDER_GUIDE_Cara Brophy  _Saturday, March 21, 2026  _0.xlsx
+++ b/prep_and_checklists/Cara Brophy  /ORDER_GUIDE_Cara Brophy  _Saturday, March 21, 2026  _0.xlsx
@@ -8,15 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/Cara Brophy  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE6111F-332E-FB41-8065-F9BDE96A9E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A86D7E-3056-7647-9579-6BE1387FD487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="1160" windowWidth="29940" windowHeight="17600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="860" windowWidth="29940" windowHeight="17600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="order_guide" sheetId="1" r:id="rId1"/>
     <sheet name="protein_order_guide" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -278,10 +291,10 @@
     <t>2oz dry aged beef hamburger</t>
   </si>
   <si>
-    <t>Pat Lafreida</t>
-  </si>
-  <si>
     <t>1 case</t>
+  </si>
+  <si>
+    <t>Pat Lafreida, 3in diameter</t>
   </si>
 </sst>
 </file>
@@ -3641,7 +3654,7 @@
     <col min="1" max="1" width="40.5" style="11" customWidth="1"/>
     <col min="2" max="2" width="13" style="11" customWidth="1"/>
     <col min="3" max="3" width="28.33203125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="20.5" customWidth="1"/>
+    <col min="4" max="4" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -3683,7 +3696,7 @@
         <v>83</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
@@ -3699,7 +3712,7 @@
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="15"/>
